--- a/assets/data/excel/baseFacilities.xlsx
+++ b/assets/data/excel/baseFacilities.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,46 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CCCCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -72,30 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,180 +413,169 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>nameZh</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>baseCost</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>costMultiplier</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>maxLevel</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>effectType</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>effectValue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>nameZh</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>英文名称</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>中文名称</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>baseCost</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>costMultiplier</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>maxLevel</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>effectType</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>effectValue</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>基础费用</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>费用倍率</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>最大等级</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>效果类型</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>效果值</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>workbench</t>
+          <t>fusion_pod</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Workbench</t>
+          <t>Fusion Pod</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>工作台</t>
+          <t>融合舱</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>增加可同时招募的驾驶员数量，每级+1</t>
+          <t>融合姬管理和强化，每级+1招募位</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -658,26 +599,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>chargers</t>
+          <t>dorms</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chargers</t>
+          <t>Dorms</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>充电桩</t>
+          <t>休眠舱</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>增加可同时招募的驾驶员数量，每级+1</t>
+          <t>融合姬恢复速度提升，每级+10%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F5" t="n">
         <v>1.5</v>
@@ -687,36 +628,36 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>recruit_slots</t>
+          <t>refresh_speed</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dorms</t>
+          <t>synthesizer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dorms</t>
+          <t>Synthesizer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>休眠舱</t>
+          <t>合成台</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>增加驾驶员的恢复速度</t>
+          <t>芯片合成成功率提升，每级+5%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F6" t="n">
         <v>1.5</v>
@@ -726,36 +667,36 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>refresh_speed</t>
+          <t>chip_synthesis_rate</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>workbench</t>
+          <t>training</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Workbench</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>工作台</t>
+          <t>训练场</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>增加可同时招募的驾驶员数量，每级+1</t>
+          <t>融合姬经验获取提升，每级+5%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F7" t="n">
         <v>1.5</v>
@@ -765,284 +706,49 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>recruit_slots</t>
+          <t>exp_rate</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>synthesizer</t>
+          <t>hacker</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Synthesizer</t>
+          <t>Hacker Terminal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>合成台</t>
+          <t>黑客终端</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>增加能量饮料的效果，每级+5%</t>
+          <t>解锁传送功能，可快速到达已探索区域</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>energy_effect</t>
+          <t>unlock_teleport</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>dorms</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Dorms</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>休眠舱</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>增加驾驶员的恢复速度</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>150</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>refresh_speed</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>training</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>训练场</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>增加驾驶员的经验获取，每级+5%</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>250</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>10</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>exp_rate</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>synthesizer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Synthesizer</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>合成台</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>增加能量饮料的效果，每级+5%</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>200</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>10</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>energy_effect</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>hacker</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Hacker</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>黑客终端</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>解锁传送功能</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>500</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>unlock_teleport</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>training</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>训练场</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>增加驾驶员的经验获取，每级+5%</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>250</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>10</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>exp_rate</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>hacker</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Hacker</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>黑客终端</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>解锁传送功能</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>500</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>unlock_teleport</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
         <v>1</v>
       </c>
     </row>
